--- a/dev-docs/task-260902-报价与核价建表与导入方案新规范/核价2 - 数据导入与表格建表.xlsx
+++ b/dev-docs/task-260902-报价与核价建表与导入方案新规范/核价2 - 数据导入与表格建表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\joii\project\cpq\dev-docs\task-260902-报价与核价建表与导入方案新规范\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23564D9-24DC-430E-AA74-FB1C60104F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9262EC88-C1C4-4DD5-9DBC-BA6D347C20AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="909" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="物料" sheetId="3" r:id="rId1"/>
@@ -1840,7 +1840,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="23.125" customWidth="1"/>
@@ -2057,9 +2057,6 @@
       <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:14" ht="16.5">
-      <c r="A10" s="11">
-        <v>3120014539</v>
-      </c>
       <c r="B10" s="13"/>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -2070,9 +2067,6 @@
       <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:14" ht="16.5">
-      <c r="A11" s="11">
-        <v>2120011658</v>
-      </c>
       <c r="B11" s="13"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -2083,9 +2077,6 @@
       <c r="I11" s="11"/>
     </row>
     <row r="12" spans="1:14" ht="16.5">
-      <c r="A12" s="11">
-        <v>2120011658</v>
-      </c>
       <c r="B12" s="13"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -2096,9 +2087,6 @@
       <c r="I12" s="11"/>
     </row>
     <row r="13" spans="1:14" ht="16.5">
-      <c r="A13" s="11">
-        <v>3110520789</v>
-      </c>
       <c r="B13" s="13"/>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -2109,9 +2097,6 @@
       <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:14" ht="16.5">
-      <c r="A14" s="11">
-        <v>3110520789</v>
-      </c>
       <c r="B14" s="13"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -2122,9 +2107,6 @@
       <c r="I14" s="11"/>
     </row>
     <row r="15" spans="1:14" ht="16.5">
-      <c r="A15" s="11">
-        <v>2120011659</v>
-      </c>
       <c r="B15" s="13"/>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
@@ -2135,9 +2117,6 @@
       <c r="I15" s="11"/>
     </row>
     <row r="16" spans="1:14" ht="16.5">
-      <c r="A16" s="11">
-        <v>2120011659</v>
-      </c>
       <c r="B16" s="13"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -2536,76 +2515,6 @@
       <c r="G55" s="11"/>
       <c r="H55" s="11"/>
       <c r="I55" s="11"/>
-    </row>
-    <row r="56" spans="2:9" ht="16.5">
-      <c r="B56" s="13"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-    </row>
-    <row r="57" spans="2:9" ht="16.5">
-      <c r="B57" s="13"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-    </row>
-    <row r="58" spans="2:9" ht="16.5">
-      <c r="B58" s="13"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11"/>
-    </row>
-    <row r="59" spans="2:9" ht="16.5">
-      <c r="B59" s="13"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-    </row>
-    <row r="60" spans="2:9" ht="16.5">
-      <c r="B60" s="13"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="11"/>
-      <c r="I60" s="11"/>
-    </row>
-    <row r="61" spans="2:9" ht="16.5">
-      <c r="B61" s="13"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-    </row>
-    <row r="62" spans="2:9" ht="16.5">
-      <c r="B62" s="13"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
